--- a/src/test/resources/testdata/updateBookingData.xlsx
+++ b/src/test/resources/testdata/updateBookingData.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Capgemini\AutomationTesting\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FCF4251-2F52-444C-B30C-D8598691DE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7D659A7E-150C-43FC-BF7C-CC4CA43B58A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{895B1010-C0D9-49E9-A70A-CA62BD6ED573}"/>
   </bookViews>
@@ -16,6 +11,7 @@
     <sheet name="updateBookingData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 

--- a/src/test/resources/testdata/updateBookingData.xlsx
+++ b/src/test/resources/testdata/updateBookingData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7D659A7E-150C-43FC-BF7C-CC4CA43B58A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{851B0097-BA69-4212-9E8F-6DD1ECD7BDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{895B1010-C0D9-49E9-A70A-CA62BD6ED573}"/>
   </bookViews>
